--- a/diseases/d108/2000-2004.xlsx
+++ b/diseases/d108/2000-2004.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19217,7 +19217,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21125,7 +21125,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22079,7 +22079,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25180,7 +25180,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28042,7 +28042,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -28996,7 +28996,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29950,7 +29950,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -30904,7 +30904,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -32812,7 +32812,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33766,7 +33766,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -36867,7 +36867,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38775,7 +38775,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -39729,7 +39729,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -41637,7 +41637,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -42591,7 +42591,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -43545,7 +43545,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -44499,7 +44499,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46407,7 +46407,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -47361,7 +47361,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48554,7 +48554,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -50462,7 +50462,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51416,7 +51416,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -52370,7 +52370,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -53324,7 +53324,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -55232,7 +55232,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -56186,7 +56186,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -57140,7 +57140,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -58094,7 +58094,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -59048,7 +59048,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
